--- a/public/templates/연구 목록 양식.xlsx
+++ b/public/templates/연구 목록 양식.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>연구시작일, 상급결재권자</t>
+          <t>연구시작일, 상급결재권자. 이 열을 지우거나 모두 비워 두면 업로드 버튼 아래에 무엇이 빠졌는지 알려 줍니다.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>첫 번째 시트만 읽습니다. 이 안내 시트는 지우지 않아도 읽지 않습니다.</t>
+          <t>꼭 있어야 하는 열이 있는 시트를 찾아 읽습니다. 이 안내 시트는 지우지 않아도 읽지 않습니다.</t>
         </is>
       </c>
     </row>

--- a/public/templates/연구 목록 양식.xlsx
+++ b/public/templates/연구 목록 양식.xlsx
@@ -574,9 +574,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -621,7 +619,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>과제 하나가 한 줄입니다. 3행의 예시 줄은 지우고 쓰세요.</t>
+          <t>과제 하나가 한 줄입니다. 3행의 예시 줄은 지우고 쓰세요. 같은 과제명이 여러 줄이면 맨 아래 줄만 씁니다.</t>
         </is>
       </c>
     </row>
@@ -669,7 +667,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2025.12.31, 2025-12-31, 20251231 모양 모두 읽습니다.</t>
+          <t>2025.12.31, 2025-12-31, 20251231 모양과 엑셀 날짜 칸 모두 읽습니다. 없는 날짜나 일까지 적지 않은 날짜(예: 2025.12)는 빈칸으로 읽습니다.</t>
         </is>
       </c>
     </row>
@@ -681,7 +679,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>과제명이 지원정보의 연구과제명과 같으면(띄어쓰기와 괄호·점 같은 기호는 무시) 그 지원자의 참여과제로 연결합니다. 연구종료일이 평가기준일 기준 최근 2년 안이면 연구책임자와 상급결재권자를 제척합니다.</t>
+          <t>과제명이 지원정보의 연구과제명과 같으면 그 지원자의 참여과제로 연결합니다. 띄어쓰기, 괄호, 가운뎃점·마침표·쉼표, 빗금, 붙임표는 무시하고 영문 대소문자와 그 밖의 기호(「」 등)는 구별합니다. 연구종료일이 평가기준일의 2년 전 같은 날 이후이면(그날 포함) 연구책임자와 상급결재권자를 제척합니다. 연구종료일이 비어 있으면 확인 필요로 남깁니다.</t>
         </is>
       </c>
     </row>
